--- a/data/lookups.xlsx
+++ b/data/lookups.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>company</t>
   </si>
@@ -37,6 +37,9 @@
     <t>BC</t>
   </si>
   <si>
+    <t>AB</t>
+  </si>
+  <si>
     <t>asset_type</t>
   </si>
   <si>
@@ -46,7 +49,10 @@
     <t>Cableway</t>
   </si>
   <si>
-    <t>#3b92d7</t>
+    <t>#ae0804</t>
+  </si>
+  <si>
+    <t>#00968a</t>
   </si>
   <si>
     <t>weight</t>
@@ -480,7 +486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -499,6 +505,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -507,12 +521,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
@@ -521,12 +535,12 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -535,7 +549,21 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +579,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -570,10 +598,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -589,25 +617,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -623,10 +651,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
